--- a/SuppXLS/Scen_fossilfuels_prices.xlsx
+++ b/SuppXLS/Scen_fossilfuels_prices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7A0F5EE-B8CF-4B62-9131-A3AFFDE6F66A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F49A33-085E-4503-9799-4FC8B01966BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="fuel_costs" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="39">
   <si>
     <t>~TFM_INS-TS</t>
   </si>
@@ -83,6 +83,9 @@
   </si>
   <si>
     <t>LimType</t>
+  </si>
+  <si>
+    <t>pset_co</t>
   </si>
   <si>
     <t>Attribute</t>
@@ -761,21 +764,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:W20"/>
+  <dimension ref="B2:X20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -785,324 +788,339 @@
       <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="4">
         <v>2025</v>
       </c>
-      <c r="F3" s="4">
+      <c r="G3" s="4">
         <v>2030</v>
       </c>
-      <c r="G3" s="4">
+      <c r="H3" s="4">
         <v>2035</v>
       </c>
-      <c r="H3" s="4">
+      <c r="I3" s="4">
         <v>2040</v>
       </c>
-      <c r="I3" s="4">
+      <c r="J3" s="4">
         <v>2045</v>
       </c>
-      <c r="J3" s="4">
+      <c r="K3" s="4">
         <v>2050</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="O3" s="4">
+      <c r="L3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P3" s="4">
         <v>2025</v>
       </c>
-      <c r="P3" s="4">
+      <c r="Q3" s="4">
         <v>2030</v>
       </c>
-      <c r="Q3" s="4">
+      <c r="R3" s="4">
         <v>2035</v>
       </c>
-      <c r="R3" s="4">
+      <c r="S3" s="4">
         <v>2040</v>
       </c>
-      <c r="S3" s="4">
+      <c r="T3" s="4">
         <v>2045</v>
       </c>
-      <c r="T3" s="4">
+      <c r="U3" s="4">
         <v>2050</v>
       </c>
-      <c r="V3" t="s">
-        <v>9</v>
-      </c>
-      <c r="W3">
+      <c r="W3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X3">
         <v>3.5999999999999998E-6</v>
       </c>
     </row>
-    <row r="4" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:24" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="6">
-        <f>O4/$W$3/1000000</f>
+      <c r="E4" t="s">
+        <v>7</v>
+      </c>
+      <c r="F4" s="6">
+        <f>P4/$X$3/1000000</f>
         <v>10</v>
       </c>
-      <c r="F4" s="6">
-        <f>P4/$W$3/1000000</f>
+      <c r="G4" s="6">
+        <f>Q4/$X$3/1000000</f>
         <v>7.8611111111111116</v>
       </c>
-      <c r="G4" s="6">
-        <f>Q4/$W$3/1000000</f>
+      <c r="H4" s="6">
+        <f>R4/$X$3/1000000</f>
         <v>5.6944444444444446</v>
       </c>
-      <c r="H4" s="6">
-        <f>R4/$W$3/1000000</f>
+      <c r="I4" s="6">
+        <f>S4/$X$3/1000000</f>
         <v>6.25</v>
       </c>
-      <c r="I4" s="6">
-        <f>S4/$W$3/1000000</f>
+      <c r="J4" s="6">
+        <f>T4/$X$3/1000000</f>
         <v>6.8055555555555562</v>
       </c>
-      <c r="J4" s="6">
-        <f>T4/$W$3/1000000</f>
+      <c r="K4" s="6">
+        <f>U4/$X$3/1000000</f>
         <v>7.3611111111111107</v>
       </c>
-      <c r="K4" t="s">
-        <v>5</v>
-      </c>
-      <c r="O4" s="13">
+      <c r="L4" t="s">
+        <v>6</v>
+      </c>
+      <c r="P4" s="13">
         <v>36</v>
       </c>
-      <c r="P4" s="13">
+      <c r="Q4" s="13">
         <v>28.3</v>
       </c>
-      <c r="Q4" s="13">
+      <c r="R4" s="13">
         <v>20.5</v>
       </c>
-      <c r="R4" s="13">
+      <c r="S4" s="13">
         <v>22.5</v>
       </c>
-      <c r="S4" s="13">
+      <c r="T4" s="13">
         <v>24.5</v>
       </c>
-      <c r="T4" s="13">
+      <c r="U4" s="13">
         <v>26.5</v>
       </c>
-      <c r="U4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="V4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:24" x14ac:dyDescent="0.25">
       <c r="D5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="6">
-        <f>O5/$W$3/1000000</f>
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" s="6">
+        <f>P5/$X$3/1000000</f>
         <v>3.6944444444444451</v>
       </c>
-      <c r="F5" s="6">
-        <f t="shared" ref="F5:F7" si="0">P5/$W$3/1000000</f>
+      <c r="G5" s="6">
+        <f t="shared" ref="G5:G7" si="0">Q5/$X$3/1000000</f>
         <v>3.2777777777777781</v>
       </c>
-      <c r="G5" s="6">
-        <f t="shared" ref="G5:G7" si="1">Q5/$W$3/1000000</f>
+      <c r="H5" s="6">
+        <f t="shared" ref="H5:H7" si="1">R5/$X$3/1000000</f>
         <v>2.8611111111111116</v>
       </c>
-      <c r="H5" s="6">
-        <f t="shared" ref="H5:H7" si="2">R5/$W$3/1000000</f>
+      <c r="I5" s="6">
+        <f t="shared" ref="I5:I7" si="2">S5/$X$3/1000000</f>
         <v>2.7222222222222223</v>
       </c>
-      <c r="I5" s="6">
-        <f t="shared" ref="I5:I7" si="3">S5/$W$3/1000000</f>
+      <c r="J5" s="6">
+        <f t="shared" ref="J5:J7" si="3">T5/$X$3/1000000</f>
         <v>2.5555555555555554</v>
       </c>
-      <c r="J5" s="6">
-        <f t="shared" ref="J5:J7" si="4">T5/$W$3/1000000</f>
+      <c r="K5" s="6">
+        <f t="shared" ref="K5:K7" si="4">U5/$X$3/1000000</f>
         <v>2.4166666666666665</v>
       </c>
-      <c r="K5" t="s">
-        <v>11</v>
-      </c>
-      <c r="O5" s="13">
+      <c r="L5" t="s">
+        <v>12</v>
+      </c>
+      <c r="P5" s="13">
         <v>13.3</v>
       </c>
-      <c r="P5" s="13">
+      <c r="Q5" s="13">
         <v>11.8</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="R5" s="13">
         <v>10.3</v>
       </c>
-      <c r="R5" s="13">
+      <c r="S5" s="13">
         <v>9.8000000000000007</v>
       </c>
-      <c r="S5" s="13">
+      <c r="T5" s="13">
         <v>9.1999999999999993</v>
       </c>
-      <c r="T5" s="13">
+      <c r="U5" s="13">
         <v>8.6999999999999993</v>
       </c>
-      <c r="U5" t="s">
-        <v>11</v>
-      </c>
-      <c r="W5">
-        <f>1/W3</f>
+      <c r="V5" t="s">
+        <v>12</v>
+      </c>
+      <c r="X5">
+        <f>1/X3</f>
         <v>277777.77777777781</v>
       </c>
     </row>
-    <row r="6" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="6">
-        <f>O6/$W$3/1000000</f>
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="6">
+        <f>P6/$X$3/1000000</f>
         <v>12.194444444444445</v>
       </c>
-      <c r="F6" s="6">
+      <c r="G6" s="6">
         <f t="shared" si="0"/>
         <v>12.27777777777778</v>
       </c>
-      <c r="G6" s="6">
+      <c r="H6" s="6">
         <f t="shared" si="1"/>
         <v>12.361111111111112</v>
       </c>
-      <c r="H6" s="6">
+      <c r="I6" s="6">
         <f t="shared" si="2"/>
         <v>12.166666666666666</v>
       </c>
-      <c r="I6" s="6">
+      <c r="J6" s="6">
         <f t="shared" si="3"/>
         <v>11.944444444444446</v>
       </c>
-      <c r="J6" s="6">
+      <c r="K6" s="6">
         <f t="shared" si="4"/>
         <v>11.75</v>
       </c>
-      <c r="K6" t="s">
-        <v>8</v>
-      </c>
-      <c r="O6" s="14">
+      <c r="L6" t="s">
+        <v>9</v>
+      </c>
+      <c r="P6" s="14">
         <v>43.9</v>
       </c>
-      <c r="P6" s="14">
+      <c r="Q6" s="14">
         <v>44.2</v>
       </c>
-      <c r="Q6" s="14">
+      <c r="R6" s="14">
         <v>44.5</v>
       </c>
-      <c r="R6" s="14">
+      <c r="S6" s="14">
         <v>43.8</v>
       </c>
-      <c r="S6" s="14">
+      <c r="T6" s="14">
         <v>43</v>
       </c>
-      <c r="T6" s="13">
+      <c r="U6" s="13">
         <v>42.3</v>
       </c>
-      <c r="U6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="V6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="2:24" x14ac:dyDescent="0.25">
       <c r="D7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="6">
+        <v>13</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" s="6">
         <v>3.1578947368421053</v>
       </c>
-      <c r="F7" s="6">
-        <f>E7*F12</f>
+      <c r="G7" s="6">
+        <f>F7*F12</f>
         <v>2.8017411950929954</v>
       </c>
-      <c r="G7" s="6">
-        <f>F7*G12</f>
+      <c r="H7" s="6">
+        <f>G7*G12</f>
         <v>2.4455876533438858</v>
       </c>
-      <c r="H7" s="6">
-        <f>G7*H12</f>
+      <c r="I7" s="6">
+        <f>H7*H12</f>
         <v>2.3268698060941828</v>
       </c>
-      <c r="I7" s="6">
-        <f>H7*I12</f>
+      <c r="J7" s="6">
+        <f>I7*I12</f>
         <v>2.1844083893945387</v>
       </c>
-      <c r="J7" s="6">
-        <f>I7*J12</f>
+      <c r="K7" s="6">
+        <f>J7*J12</f>
         <v>2.0656905421448357</v>
       </c>
-      <c r="K7" t="s">
-        <v>12</v>
-      </c>
-      <c r="O7">
+      <c r="L7" t="s">
+        <v>13</v>
+      </c>
+      <c r="P7">
         <v>3.1578947368421053</v>
       </c>
-      <c r="P7">
-        <f>O7*F12</f>
+      <c r="Q7">
+        <f>P7*F12</f>
         <v>2.8017411950929954</v>
       </c>
-      <c r="Q7">
-        <f>P7*G12</f>
+      <c r="R7">
+        <f>Q7*G12</f>
         <v>2.4455876533438858</v>
       </c>
-      <c r="R7">
-        <f>Q7*H12</f>
+      <c r="S7">
+        <f>R7*H12</f>
         <v>2.3268698060941828</v>
       </c>
-      <c r="S7">
-        <f>R7*I12</f>
+      <c r="T7">
+        <f>S7*I12</f>
         <v>2.1844083893945387</v>
       </c>
-      <c r="T7">
-        <f>S7*J12</f>
+      <c r="U7">
+        <f>T7*J12</f>
         <v>2.0656905421448357</v>
       </c>
-      <c r="U7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="V7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="2:24" x14ac:dyDescent="0.25">
       <c r="F12" s="15">
-        <f>P5/O5</f>
+        <f>Q5/P5</f>
         <v>0.88721804511278191</v>
       </c>
       <c r="G12" s="15">
-        <f>Q5/P5</f>
+        <f>R5/Q5</f>
         <v>0.8728813559322034</v>
       </c>
       <c r="H12" s="15">
-        <f>R5/Q5</f>
+        <f>S5/R5</f>
         <v>0.95145631067961167</v>
       </c>
       <c r="I12" s="15">
-        <f>S5/R5</f>
+        <f>T5/S5</f>
         <v>0.93877551020408145</v>
       </c>
       <c r="J12" s="15">
-        <f>T5/S5</f>
+        <f>U5/T5</f>
         <v>0.94565217391304346</v>
       </c>
     </row>
     <row r="20" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" s="6">
-        <f>O20/$W$3/1000000</f>
+        <f>O20/$X$3/1000000</f>
         <v>12.720000000000002</v>
       </c>
       <c r="F20" s="6">
-        <f>P20/$W$3/1000000</f>
+        <f>P20/$X$3/1000000</f>
         <v>13.333333333333334</v>
       </c>
       <c r="G20" s="6">
-        <f>Q20/$W$3/1000000</f>
+        <f>Q20/$X$3/1000000</f>
         <v>13.888888888888889</v>
       </c>
       <c r="H20" s="6">
-        <f>R20/$W$3/1000000</f>
+        <f>R20/$X$3/1000000</f>
         <v>14.444444444444446</v>
       </c>
       <c r="I20" s="6">
-        <f>S20/$W$3/1000000</f>
+        <f>S20/$X$3/1000000</f>
         <v>15</v>
       </c>
       <c r="J20" s="6">
-        <f>T20/$W$3/1000000</f>
+        <f>T20/$X$3/1000000</f>
         <v>15.277777777777779</v>
       </c>
       <c r="K20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O20" s="5">
         <v>45.792000000000002</v>
@@ -1138,49 +1156,49 @@
   <sheetData>
     <row r="5" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="N5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="Q5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="2:31" x14ac:dyDescent="0.25">
@@ -1201,13 +1219,13 @@
         <v>3600000</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H6">
         <v>3412142</v>
       </c>
       <c r="J6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>25</v>
@@ -1241,13 +1259,13 @@
     </row>
     <row r="7" spans="2:31" x14ac:dyDescent="0.25">
       <c r="G7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H7" s="9">
         <v>588235</v>
       </c>
       <c r="J7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K7">
         <v>4</v>
@@ -1277,13 +1295,13 @@
     </row>
     <row r="8" spans="2:31" x14ac:dyDescent="0.25">
       <c r="G8" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H8">
         <v>150000</v>
       </c>
       <c r="J8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>39</v>
@@ -1313,7 +1331,7 @@
     </row>
     <row r="9" spans="2:31" x14ac:dyDescent="0.25">
       <c r="J9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L9">
         <v>12.72</v>
@@ -1341,7 +1359,7 @@
     </row>
     <row r="12" spans="2:31" x14ac:dyDescent="0.25">
       <c r="P12" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q12" s="10"/>
       <c r="R12" s="10"/>
@@ -1349,14 +1367,14 @@
       <c r="T12" s="10"/>
       <c r="U12" s="10"/>
       <c r="V12" s="10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W12" s="10"/>
       <c r="X12" s="10"/>
       <c r="Y12" s="10"/>
       <c r="Z12" s="10"/>
       <c r="AA12" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AB12" s="10"/>
       <c r="AC12" s="10"/>
@@ -1415,7 +1433,7 @@
     </row>
     <row r="14" spans="2:31" x14ac:dyDescent="0.25">
       <c r="O14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P14" s="5">
         <v>36</v>
@@ -1477,7 +1495,7 @@
     </row>
     <row r="15" spans="2:31" x14ac:dyDescent="0.25">
       <c r="O15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P15">
         <v>13.3</v>
@@ -1539,7 +1557,7 @@
     </row>
     <row r="16" spans="2:31" x14ac:dyDescent="0.25">
       <c r="O16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P16">
         <v>43.9</v>

--- a/SuppXLS/Scen_fossilfuels_prices.xlsx
+++ b/SuppXLS/Scen_fossilfuels_prices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\PycharmProjects\ee-times\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7F49A33-085E-4503-9799-4FC8B01966BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D16E5E5-38A1-4A8F-98A0-5C15FC701EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-5220" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="fuel_costs" sheetId="1" r:id="rId1"/>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="46">
   <si>
     <t>~TFM_INS-TS</t>
   </si>
@@ -85,15 +85,9 @@
     <t>LimType</t>
   </si>
   <si>
-    <t>pset_co</t>
-  </si>
-  <si>
     <t>Attribute</t>
   </si>
   <si>
-    <t>Commodity</t>
-  </si>
-  <si>
     <t>Gas</t>
   </si>
   <si>
@@ -191,6 +185,33 @@
   </si>
   <si>
     <t>Nafta, €/MWh</t>
+  </si>
+  <si>
+    <t>cost</t>
+  </si>
+  <si>
+    <t>pset_pn</t>
+  </si>
+  <si>
+    <t>MINSHL1</t>
+  </si>
+  <si>
+    <t>IMPOIL1</t>
+  </si>
+  <si>
+    <t>IMPCOA1</t>
+  </si>
+  <si>
+    <t>IMPGAS1</t>
+  </si>
+  <si>
+    <t>EXPGAS1</t>
+  </si>
+  <si>
+    <t>EXPCOA1</t>
+  </si>
+  <si>
+    <t>EXPOIL1</t>
   </si>
 </sst>
 </file>
@@ -201,7 +222,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -234,12 +255,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -341,21 +356,21 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -786,10 +801,10 @@
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>3</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="F3" s="4">
         <v>2025</v>
@@ -809,9 +824,7 @@
       <c r="K3" s="4">
         <v>2050</v>
       </c>
-      <c r="L3" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="L3" s="3"/>
       <c r="P3" s="4">
         <v>2025</v>
       </c>
@@ -831,7 +844,7 @@
         <v>2050</v>
       </c>
       <c r="W3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X3">
         <v>3.5999999999999998E-6</v>
@@ -839,10 +852,10 @@
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.25">
       <c r="D4" t="s">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="F4" s="6">
         <f>P4/$X$3/1000000</f>
@@ -868,85 +881,79 @@
         <f>U4/$X$3/1000000</f>
         <v>7.3611111111111107</v>
       </c>
-      <c r="L4" t="s">
-        <v>6</v>
-      </c>
-      <c r="P4" s="13">
+      <c r="P4" s="10">
         <v>36</v>
       </c>
-      <c r="Q4" s="13">
+      <c r="Q4" s="10">
         <v>28.3</v>
       </c>
-      <c r="R4" s="13">
+      <c r="R4" s="10">
         <v>20.5</v>
       </c>
-      <c r="S4" s="13">
+      <c r="S4" s="10">
         <v>22.5</v>
       </c>
-      <c r="T4" s="13">
+      <c r="T4" s="10">
         <v>24.5</v>
       </c>
-      <c r="U4" s="13">
+      <c r="U4" s="10">
         <v>26.5</v>
       </c>
       <c r="V4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.25">
       <c r="D5" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="F5" s="6">
         <f>P5/$X$3/1000000</f>
         <v>3.6944444444444451</v>
       </c>
       <c r="G5" s="6">
-        <f t="shared" ref="G5:G7" si="0">Q5/$X$3/1000000</f>
+        <f>Q5/$X$3/1000000</f>
         <v>3.2777777777777781</v>
       </c>
       <c r="H5" s="6">
-        <f t="shared" ref="H5:H7" si="1">R5/$X$3/1000000</f>
+        <f>R5/$X$3/1000000</f>
         <v>2.8611111111111116</v>
       </c>
       <c r="I5" s="6">
-        <f t="shared" ref="I5:I7" si="2">S5/$X$3/1000000</f>
+        <f>S5/$X$3/1000000</f>
         <v>2.7222222222222223</v>
       </c>
       <c r="J5" s="6">
-        <f t="shared" ref="J5:J7" si="3">T5/$X$3/1000000</f>
+        <f>T5/$X$3/1000000</f>
         <v>2.5555555555555554</v>
       </c>
       <c r="K5" s="6">
-        <f t="shared" ref="K5:K7" si="4">U5/$X$3/1000000</f>
+        <f>U5/$X$3/1000000</f>
         <v>2.4166666666666665</v>
       </c>
-      <c r="L5" t="s">
-        <v>12</v>
-      </c>
-      <c r="P5" s="13">
+      <c r="P5" s="10">
         <v>13.3</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="Q5" s="10">
         <v>11.8</v>
       </c>
-      <c r="R5" s="13">
+      <c r="R5" s="10">
         <v>10.3</v>
       </c>
-      <c r="S5" s="13">
+      <c r="S5" s="10">
         <v>9.8000000000000007</v>
       </c>
-      <c r="T5" s="13">
+      <c r="T5" s="10">
         <v>9.1999999999999993</v>
       </c>
-      <c r="U5" s="13">
+      <c r="U5" s="10">
         <v>8.6999999999999993</v>
       </c>
       <c r="V5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="X5">
         <f>1/X3</f>
@@ -955,172 +962,270 @@
     </row>
     <row r="6" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D6" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="F6" s="6">
         <f>P6/$X$3/1000000</f>
         <v>12.194444444444445</v>
       </c>
       <c r="G6" s="6">
+        <f>Q6/$X$3/1000000</f>
+        <v>12.27777777777778</v>
+      </c>
+      <c r="H6" s="6">
+        <f>R6/$X$3/1000000</f>
+        <v>12.361111111111112</v>
+      </c>
+      <c r="I6" s="6">
+        <f>S6/$X$3/1000000</f>
+        <v>12.166666666666666</v>
+      </c>
+      <c r="J6" s="6">
+        <f>T6/$X$3/1000000</f>
+        <v>11.944444444444446</v>
+      </c>
+      <c r="K6" s="6">
+        <f>U6/$X$3/1000000</f>
+        <v>11.75</v>
+      </c>
+      <c r="P6" s="11">
+        <v>43.9</v>
+      </c>
+      <c r="Q6" s="11">
+        <v>44.2</v>
+      </c>
+      <c r="R6" s="11">
+        <v>44.5</v>
+      </c>
+      <c r="S6" s="11">
+        <v>43.8</v>
+      </c>
+      <c r="T6" s="11">
+        <v>43</v>
+      </c>
+      <c r="U6" s="10">
+        <v>42.3</v>
+      </c>
+      <c r="V6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="6">
+        <v>3.1578947368421053</v>
+      </c>
+      <c r="G7" s="6">
+        <f>F7*F17</f>
+        <v>2.8017411950929954</v>
+      </c>
+      <c r="H7" s="6">
+        <f>G7*G17</f>
+        <v>2.4455876533438858</v>
+      </c>
+      <c r="I7" s="6">
+        <f>H7*H17</f>
+        <v>2.3268698060941828</v>
+      </c>
+      <c r="J7" s="6">
+        <f>I7*I17</f>
+        <v>2.1844083893945387</v>
+      </c>
+      <c r="K7" s="6">
+        <f>J7*J17</f>
+        <v>2.0656905421448357</v>
+      </c>
+      <c r="P7">
+        <v>3.1578947368421053</v>
+      </c>
+      <c r="Q7">
+        <f>P7*F17</f>
+        <v>2.8017411950929954</v>
+      </c>
+      <c r="R7">
+        <f>Q7*G17</f>
+        <v>2.4455876533438858</v>
+      </c>
+      <c r="S7">
+        <f>R7*H17</f>
+        <v>2.3268698060941828</v>
+      </c>
+      <c r="T7">
+        <f>S7*I17</f>
+        <v>2.1844083893945387</v>
+      </c>
+      <c r="U7">
+        <f>T7*J17</f>
+        <v>2.0656905421448357</v>
+      </c>
+      <c r="V7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="6">
+        <f>F4</f>
+        <v>10</v>
+      </c>
+      <c r="G8" s="6">
+        <f t="shared" ref="G8:K8" si="0">G4</f>
+        <v>7.8611111111111116</v>
+      </c>
+      <c r="H8" s="6">
         <f t="shared" si="0"/>
+        <v>5.6944444444444446</v>
+      </c>
+      <c r="I8" s="6">
+        <f t="shared" si="0"/>
+        <v>6.25</v>
+      </c>
+      <c r="J8" s="6">
+        <f t="shared" si="0"/>
+        <v>6.8055555555555562</v>
+      </c>
+      <c r="K8" s="6">
+        <f t="shared" si="0"/>
+        <v>7.3611111111111107</v>
+      </c>
+    </row>
+    <row r="9" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="6">
+        <f t="shared" ref="F9:K9" si="1">F5</f>
+        <v>3.6944444444444451</v>
+      </c>
+      <c r="G9" s="6">
+        <f t="shared" si="1"/>
+        <v>3.2777777777777781</v>
+      </c>
+      <c r="H9" s="6">
+        <f t="shared" si="1"/>
+        <v>2.8611111111111116</v>
+      </c>
+      <c r="I9" s="6">
+        <f t="shared" si="1"/>
+        <v>2.7222222222222223</v>
+      </c>
+      <c r="J9" s="6">
+        <f t="shared" si="1"/>
+        <v>2.5555555555555554</v>
+      </c>
+      <c r="K9" s="6">
+        <f t="shared" si="1"/>
+        <v>2.4166666666666665</v>
+      </c>
+    </row>
+    <row r="10" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="D10" t="s">
+        <v>45</v>
+      </c>
+      <c r="E10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="6">
+        <f t="shared" ref="F10:K10" si="2">F6</f>
+        <v>12.194444444444445</v>
+      </c>
+      <c r="G10" s="6">
+        <f t="shared" si="2"/>
         <v>12.27777777777778</v>
       </c>
-      <c r="H6" s="6">
-        <f t="shared" si="1"/>
+      <c r="H10" s="6">
+        <f t="shared" si="2"/>
         <v>12.361111111111112</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I10" s="6">
         <f t="shared" si="2"/>
         <v>12.166666666666666</v>
       </c>
-      <c r="J6" s="6">
-        <f t="shared" si="3"/>
+      <c r="J10" s="6">
+        <f t="shared" si="2"/>
         <v>11.944444444444446</v>
       </c>
-      <c r="K6" s="6">
-        <f t="shared" si="4"/>
+      <c r="K10" s="6">
+        <f t="shared" si="2"/>
         <v>11.75</v>
       </c>
-      <c r="L6" t="s">
-        <v>9</v>
-      </c>
-      <c r="P6" s="14">
-        <v>43.9</v>
-      </c>
-      <c r="Q6" s="14">
-        <v>44.2</v>
-      </c>
-      <c r="R6" s="14">
-        <v>44.5</v>
-      </c>
-      <c r="S6" s="14">
-        <v>43.8</v>
-      </c>
-      <c r="T6" s="14">
-        <v>43</v>
-      </c>
-      <c r="U6" s="13">
-        <v>42.3</v>
-      </c>
-      <c r="V6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="D7" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="6">
-        <v>3.1578947368421053</v>
-      </c>
-      <c r="G7" s="6">
-        <f>F7*F12</f>
-        <v>2.8017411950929954</v>
-      </c>
-      <c r="H7" s="6">
-        <f>G7*G12</f>
-        <v>2.4455876533438858</v>
-      </c>
-      <c r="I7" s="6">
-        <f>H7*H12</f>
-        <v>2.3268698060941828</v>
-      </c>
-      <c r="J7" s="6">
-        <f>I7*I12</f>
-        <v>2.1844083893945387</v>
-      </c>
-      <c r="K7" s="6">
-        <f>J7*J12</f>
-        <v>2.0656905421448357</v>
-      </c>
-      <c r="L7" t="s">
-        <v>13</v>
-      </c>
-      <c r="P7">
-        <v>3.1578947368421053</v>
-      </c>
-      <c r="Q7">
-        <f>P7*F12</f>
-        <v>2.8017411950929954</v>
-      </c>
-      <c r="R7">
-        <f>Q7*G12</f>
-        <v>2.4455876533438858</v>
-      </c>
-      <c r="S7">
-        <f>R7*H12</f>
-        <v>2.3268698060941828</v>
-      </c>
-      <c r="T7">
-        <f>S7*I12</f>
-        <v>2.1844083893945387</v>
-      </c>
-      <c r="U7">
-        <f>T7*J12</f>
-        <v>2.0656905421448357</v>
-      </c>
-      <c r="V7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="F12" s="15">
+    </row>
+    <row r="11" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+    </row>
+    <row r="17" spans="4:20" x14ac:dyDescent="0.25">
+      <c r="F17" s="12">
         <f>Q5/P5</f>
         <v>0.88721804511278191</v>
       </c>
-      <c r="G12" s="15">
+      <c r="G17" s="12">
         <f>R5/Q5</f>
         <v>0.8728813559322034</v>
       </c>
-      <c r="H12" s="15">
+      <c r="H17" s="12">
         <f>S5/R5</f>
         <v>0.95145631067961167</v>
       </c>
-      <c r="I12" s="15">
+      <c r="I17" s="12">
         <f>T5/S5</f>
         <v>0.93877551020408145</v>
       </c>
-      <c r="J12" s="15">
+      <c r="J17" s="12">
         <f>U5/T5</f>
         <v>0.94565217391304346</v>
       </c>
     </row>
     <row r="20" spans="4:20" x14ac:dyDescent="0.25">
       <c r="D20" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E20" s="6">
-        <f>O20/$X$3/1000000</f>
+        <f t="shared" ref="E20:J20" si="3">O20/$X$3/1000000</f>
         <v>12.720000000000002</v>
       </c>
       <c r="F20" s="6">
-        <f>P20/$X$3/1000000</f>
+        <f t="shared" si="3"/>
         <v>13.333333333333334</v>
       </c>
       <c r="G20" s="6">
-        <f>Q20/$X$3/1000000</f>
+        <f t="shared" si="3"/>
         <v>13.888888888888889</v>
       </c>
       <c r="H20" s="6">
-        <f>R20/$X$3/1000000</f>
+        <f t="shared" si="3"/>
         <v>14.444444444444446</v>
       </c>
       <c r="I20" s="6">
-        <f>S20/$X$3/1000000</f>
+        <f t="shared" si="3"/>
         <v>15</v>
       </c>
       <c r="J20" s="6">
-        <f>T20/$X$3/1000000</f>
+        <f t="shared" si="3"/>
         <v>15.277777777777779</v>
       </c>
       <c r="K20" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O20" s="5">
         <v>45.792000000000002</v>
@@ -1156,49 +1261,49 @@
   <sheetData>
     <row r="5" spans="2:31" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
         <v>14</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" t="s">
+      <c r="J5" t="s">
         <v>17</v>
       </c>
-      <c r="F5" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="K5" t="s">
         <v>18</v>
       </c>
-      <c r="J5" t="s">
+      <c r="L5" t="s">
         <v>19</v>
       </c>
-      <c r="K5" t="s">
+      <c r="M5" t="s">
         <v>20</v>
       </c>
-      <c r="L5" t="s">
+      <c r="N5" t="s">
         <v>21</v>
       </c>
-      <c r="M5" t="s">
+      <c r="O5" t="s">
         <v>22</v>
       </c>
-      <c r="N5" t="s">
+      <c r="P5" t="s">
         <v>23</v>
       </c>
-      <c r="O5" t="s">
+      <c r="Q5" t="s">
         <v>24</v>
       </c>
-      <c r="P5" t="s">
+      <c r="R5" t="s">
         <v>25</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>26</v>
-      </c>
-      <c r="R5" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="6" spans="2:31" x14ac:dyDescent="0.25">
@@ -1219,13 +1324,13 @@
         <v>3600000</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="H6">
         <v>3412142</v>
       </c>
       <c r="J6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K6">
         <v>25</v>
@@ -1242,14 +1347,14 @@
         <f>L6*F6</f>
         <v>14705882.352941176</v>
       </c>
-      <c r="O6" s="7">
+      <c r="O6" s="13">
         <v>0.9244</v>
       </c>
       <c r="P6" s="6">
         <f>M6*$AH$14</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="8">
+      <c r="Q6" s="14">
         <v>2.3E-2</v>
       </c>
       <c r="R6" s="5">
@@ -1259,13 +1364,13 @@
     </row>
     <row r="7" spans="2:31" x14ac:dyDescent="0.25">
       <c r="G7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="9">
+        <v>27</v>
+      </c>
+      <c r="H7" s="7">
         <v>588235</v>
       </c>
       <c r="J7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K7">
         <v>4</v>
@@ -1282,12 +1387,12 @@
         <f>L7*F6</f>
         <v>13648566.532770494</v>
       </c>
-      <c r="O7" s="7"/>
+      <c r="O7" s="13"/>
       <c r="P7" s="6">
         <f t="shared" ref="P7:P9" si="0">M7*$AH$14</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="8"/>
+      <c r="Q7" s="14"/>
       <c r="R7" s="5">
         <f t="shared" ref="R7:R9" si="1">P7*(1+Q7)</f>
         <v>0</v>
@@ -1295,13 +1400,13 @@
     </row>
     <row r="8" spans="2:31" x14ac:dyDescent="0.25">
       <c r="G8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H8">
         <v>150000</v>
       </c>
       <c r="J8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K8">
         <v>39</v>
@@ -1318,12 +1423,12 @@
         <f>L8*F6</f>
         <v>5592734.2256214144</v>
       </c>
-      <c r="O8" s="7"/>
+      <c r="O8" s="13"/>
       <c r="P8" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q8" s="8"/>
+      <c r="Q8" s="14"/>
       <c r="R8" s="5">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1331,7 +1436,7 @@
     </row>
     <row r="9" spans="2:31" x14ac:dyDescent="0.25">
       <c r="J9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L9">
         <v>12.72</v>
@@ -1340,12 +1445,12 @@
         <f>L9*E6</f>
         <v>45.792000000000002</v>
       </c>
-      <c r="O9" s="7"/>
+      <c r="O9" s="13"/>
       <c r="P9" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q9" s="8"/>
+      <c r="Q9" s="14"/>
       <c r="R9" s="5">
         <f t="shared" si="1"/>
         <v>0</v>
@@ -1358,28 +1463,28 @@
       </c>
     </row>
     <row r="12" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="P12" s="10" t="s">
+      <c r="P12" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q12" s="15"/>
+      <c r="R12" s="15"/>
+      <c r="S12" s="15"/>
+      <c r="T12" s="15"/>
+      <c r="U12" s="15"/>
+      <c r="V12" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="W12" s="15"/>
+      <c r="X12" s="15"/>
+      <c r="Y12" s="15"/>
+      <c r="Z12" s="15"/>
+      <c r="AA12" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="10"/>
-      <c r="S12" s="10"/>
-      <c r="T12" s="10"/>
-      <c r="U12" s="10"/>
-      <c r="V12" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="W12" s="10"/>
-      <c r="X12" s="10"/>
-      <c r="Y12" s="10"/>
-      <c r="Z12" s="10"/>
-      <c r="AA12" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="AB12" s="10"/>
-      <c r="AC12" s="10"/>
-      <c r="AD12" s="10"/>
-      <c r="AE12" s="10"/>
+      <c r="AB12" s="15"/>
+      <c r="AC12" s="15"/>
+      <c r="AD12" s="15"/>
+      <c r="AE12" s="15"/>
     </row>
     <row r="13" spans="2:31" x14ac:dyDescent="0.25">
       <c r="P13">
@@ -1397,7 +1502,7 @@
       <c r="T13">
         <v>2045</v>
       </c>
-      <c r="U13" s="11">
+      <c r="U13" s="8">
         <v>2050</v>
       </c>
       <c r="V13">
@@ -1412,7 +1517,7 @@
       <c r="Y13">
         <v>2045</v>
       </c>
-      <c r="Z13" s="11">
+      <c r="Z13" s="8">
         <v>2050</v>
       </c>
       <c r="AA13">
@@ -1433,7 +1538,7 @@
     </row>
     <row r="14" spans="2:31" x14ac:dyDescent="0.25">
       <c r="O14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="P14" s="5">
         <v>36</v>
@@ -1453,7 +1558,7 @@
         <f>$R$14+((T13-$R$13)/($U$13-$R$13))*($U$14-$R$14)</f>
         <v>24.5</v>
       </c>
-      <c r="U14" s="11">
+      <c r="U14" s="8">
         <v>26.5</v>
       </c>
       <c r="V14" s="5">
@@ -1471,7 +1576,7 @@
         <f>$W$14+((Y13-$W$13)/($Z$13-$W$13))*($Z$14-$W$14)</f>
         <v>31.833333333333332</v>
       </c>
-      <c r="Z14" s="11">
+      <c r="Z14" s="8">
         <v>33.4</v>
       </c>
       <c r="AA14" s="5">
@@ -1495,7 +1600,7 @@
     </row>
     <row r="15" spans="2:31" x14ac:dyDescent="0.25">
       <c r="O15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="P15">
         <v>13.3</v>
@@ -1515,7 +1620,7 @@
         <f>$R$15+((T13-$R$13)/($U$13-$R$13))*($U$15-$R$15)</f>
         <v>9.2333333333333325</v>
       </c>
-      <c r="U15" s="11">
+      <c r="U15" s="8">
         <v>8.6999999999999993</v>
       </c>
       <c r="V15" s="5">
@@ -1533,7 +1638,7 @@
         <f>$W$15+((Y13-$W$13)/($Z$13-$W$13))*($Z$15-$W$15)</f>
         <v>11.333333333333334</v>
       </c>
-      <c r="Z15" s="11">
+      <c r="Z15" s="8">
         <v>10.9</v>
       </c>
       <c r="AA15" s="5">
@@ -1557,7 +1662,7 @@
     </row>
     <row r="16" spans="2:31" x14ac:dyDescent="0.25">
       <c r="O16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="P16">
         <v>43.9</v>
@@ -1577,7 +1682,7 @@
         <f>$R$16+((T13-$R$13)/($U$13-$R$13))*($U$16-$R$16)</f>
         <v>43.033333333333331</v>
       </c>
-      <c r="U16" s="11">
+      <c r="U16" s="8">
         <v>42.3</v>
       </c>
       <c r="V16" s="5">
@@ -1595,7 +1700,7 @@
         <f>$W$16+((Y13-$W$13)/($Z$13-$W$13))*($Z$16-$W$16)</f>
         <v>55.833333333333336</v>
       </c>
-      <c r="Z16" s="12">
+      <c r="Z16" s="9">
         <v>59</v>
       </c>
       <c r="AA16" s="5">
